--- a/docs/template_base_dados_analises_diario.xlsx
+++ b/docs/template_base_dados_analises_diario.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Biomarcadores" sheetId="1" r:id="R4410fe44a8b34bce"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Analises" sheetId="2" r:id="Ra2c5f10055ec4422"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Comportamentos" sheetId="3" r:id="R33106c09376a4944"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Diario_Comportamentos" sheetId="4" r:id="R505fcfef63ec4cb2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Impacto" sheetId="5" r:id="R089468a599994f46"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Biomarcadores" sheetId="1" r:id="R10a3fb707d674374"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Analises" sheetId="2" r:id="R63833b6677f34ea7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Comportamentos" sheetId="3" r:id="R0cc7391e964048f2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Diario_Comportamentos" sheetId="4" r:id="R9855f7f4009a44dc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Impacto" sheetId="5" r:id="Rb566b66e312d469c"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1010,10 +1010,12 @@
       <x:c r="E22" s="8" t="str">
         <x:v>Ureia depois da sessão de diálise.</x:v>
       </x:c>
-      <x:c r="F22" s="8" t="str"/>
-      <x:c r="G22" s="8" t="str"/>
-      <x:c r="H22" s="8" t="str"/>
-      <x:c r="I22" s="8" t="str"/>
+      <x:c r="F22" s="8"/>
+      <x:c r="G22" s="8" t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="H22" s="8"/>
+      <x:c r="I22" s="8"/>
       <x:c r="J22" s="8" t="str">
         <x:v>menor</x:v>
       </x:c>
@@ -3879,7 +3881,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rea6b0956f7cd495b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdc5f685923d3494f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6559,7 +6561,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R275d85369af84736"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R55cd7d4e75f14d55"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8195,7 +8197,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7518150b7d2241de"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd2a36efa393f4225"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10696,7 +10698,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb18a6e33eec149b0"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdc55b27042064aa9"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -12742,7 +12744,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R923deefaeeda4b37"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R21ae6d1028794fa5"/>
   </x:tableParts>
 </x:worksheet>
 </file>